--- a/base/StructureDefinition-SGGraphDefinition.xlsx
+++ b/base/StructureDefinition-SGGraphDefinition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="333">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -355,7 +355,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -450,10 +450,14 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: Potential target for the link (new)</t>
+  </si>
+  <si>
+    <t>R5: `GraphDefinition.node` (new:BackboneElement)</t>
+  </si>
+  <si>
+    <t>Element `GraphDefinition.node` has a context of GraphDefinition based on following the parent source element upwards and mapping to `GraphDefinition`.
+Element `GraphDefinition.node` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -725,7 +729,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -770,7 +774,7 @@
     <t>GraphDefinition.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1364,17 +1368,17 @@
   <dimension ref="A1:AN53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.83203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="54.83203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.84765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.84765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.33984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="68.78125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1383,26 +1387,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="60.53125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="48.546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="53.55078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.48828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.34375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.67578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2431,7 +2435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>136</v>
       </c>
@@ -2469,7 +2473,9 @@
       <c r="M10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>19</v>
@@ -2527,13 +2533,13 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>19</v>
@@ -2547,14 +2553,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2576,16 +2582,16 @@
         <v>129</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>19</v>
@@ -2634,7 +2640,7 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2663,10 +2669,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2692,16 +2698,16 @@
         <v>98</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -2750,7 +2756,7 @@
         <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2768,10 +2774,10 @@
         <v>19</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>19</v>
@@ -2779,10 +2785,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2805,16 +2811,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2864,7 +2870,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2882,21 +2888,21 @@
         <v>19</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2919,19 +2925,19 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>19</v>
@@ -2980,7 +2986,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>84</v>
@@ -2989,7 +2995,7 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>96</v>
@@ -3007,12 +3013,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3038,13 +3044,13 @@
         <v>104</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3070,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -3094,7 +3100,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>84</v>
@@ -3112,10 +3118,10 @@
         <v>19</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>19</v>
@@ -3123,10 +3129,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3149,19 +3155,19 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3210,7 +3216,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3228,10 +3234,10 @@
         <v>19</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>19</v>
@@ -3239,14 +3245,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3265,16 +3271,16 @@
         <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3324,7 +3330,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3342,10 +3348,10 @@
         <v>19</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>19</v>
@@ -3353,10 +3359,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3379,19 +3385,19 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -3440,7 +3446,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3458,10 +3464,10 @@
         <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>19</v>
@@ -3469,10 +3475,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3495,16 +3501,16 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3554,7 +3560,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3572,7 +3578,7 @@
         <v>19</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>19</v>
@@ -3583,10 +3589,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3609,16 +3615,16 @@
         <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3668,7 +3674,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3686,7 +3692,7 @@
         <v>19</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>19</v>
@@ -3697,10 +3703,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3723,19 +3729,19 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>19</v>
@@ -3784,7 +3790,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3802,7 +3808,7 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>19</v>
@@ -3813,10 +3819,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3839,16 +3845,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3874,13 +3880,13 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
@@ -3898,7 +3904,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3916,7 +3922,7 @@
         <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>19</v>
@@ -3927,10 +3933,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3953,16 +3959,16 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4012,7 +4018,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4030,21 +4036,21 @@
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4070,10 +4076,10 @@
         <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4100,13 +4106,13 @@
         <v>19</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>19</v>
@@ -4124,7 +4130,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>84</v>
@@ -4153,10 +4159,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4179,16 +4185,16 @@
         <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4238,7 +4244,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4267,10 +4273,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4293,13 +4299,13 @@
         <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4350,7 +4356,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4379,10 +4385,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4405,13 +4411,13 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4462,7 +4468,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4491,10 +4497,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4572,7 +4578,7 @@
         <v>133</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4601,13 +4607,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>19</v>
@@ -4629,13 +4635,13 @@
         <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>130</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4686,7 +4692,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4695,7 +4701,7 @@
         <v>77</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>135</v>
@@ -4715,13 +4721,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>19</v>
@@ -4743,13 +4749,13 @@
         <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>130</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4800,7 +4806,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4809,7 +4815,7 @@
         <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>135</v>
@@ -4829,14 +4835,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4858,16 +4864,16 @@
         <v>129</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -4916,7 +4922,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4945,10 +4951,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4971,16 +4977,16 @@
         <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5030,7 +5036,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5059,10 +5065,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5085,13 +5091,13 @@
         <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5142,7 +5148,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5171,10 +5177,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5197,13 +5203,13 @@
         <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5254,7 +5260,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5283,10 +5289,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5309,13 +5315,13 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5366,7 +5372,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5395,10 +5401,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5421,13 +5427,13 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5478,7 +5484,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5507,10 +5513,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5533,13 +5539,13 @@
         <v>19</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5590,7 +5596,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5619,10 +5625,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5645,13 +5651,13 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5702,7 +5708,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5731,14 +5737,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5760,13 +5766,13 @@
         <v>129</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5816,7 +5822,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5845,14 +5851,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5874,16 +5880,16 @@
         <v>129</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -5932,7 +5938,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5961,10 +5967,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5990,10 +5996,10 @@
         <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6020,13 +6026,13 @@
         <v>19</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>19</v>
@@ -6044,7 +6050,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -6073,10 +6079,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6099,16 +6105,16 @@
         <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6158,7 +6164,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6187,10 +6193,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6213,13 +6219,13 @@
         <v>19</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6270,7 +6276,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6299,10 +6305,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6325,13 +6331,13 @@
         <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6382,7 +6388,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6411,10 +6417,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6437,13 +6443,13 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6494,7 +6500,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6523,14 +6529,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6552,13 +6558,13 @@
         <v>129</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6608,7 +6614,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6637,14 +6643,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6666,16 +6672,16 @@
         <v>129</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -6724,7 +6730,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6753,10 +6759,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6782,13 +6788,13 @@
         <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6814,13 +6820,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -6838,7 +6844,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -6867,10 +6873,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6896,10 +6902,10 @@
         <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6926,13 +6932,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -6950,7 +6956,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
@@ -6979,10 +6985,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7008,10 +7014,10 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7038,13 +7044,13 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
@@ -7062,7 +7068,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>84</v>
@@ -7091,10 +7097,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7117,13 +7123,13 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7174,7 +7180,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7203,10 +7209,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7229,13 +7235,13 @@
         <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7286,7 +7292,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7315,10 +7321,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7344,10 +7350,10 @@
         <v>78</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7398,7 +7404,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7427,12 +7433,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN53">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
